--- a/backend/excel-templates/defense-showcase/04_master_supervisor_users.xlsx
+++ b/backend/excel-templates/defense-showcase/04_master_supervisor_users.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Supervisors" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,79 +397,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>firstName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>lastName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>designation</v>
+      </c>
+      <c r="D1" t="str">
         <v>email</v>
       </c>
-      <c r="B1" t="str">
+      <c r="E1" t="str">
         <v>password</v>
-      </c>
-      <c r="C1" t="str">
-        <v>firstName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>lastName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>designation</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Subarna</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Shakya</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Prof. Dr.</v>
+      </c>
+      <c r="D2" t="str">
         <v>subarna.shakya@pcampus.edu.np</v>
       </c>
-      <c r="B2" t="str">
+      <c r="E2" t="str">
         <v>Test@123Password</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Subarna</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Shakya</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Prof. Dr.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Nanda Bikram</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Adhikari</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Prof. Dr.</v>
+      </c>
+      <c r="D3" t="str">
         <v>nanda.adhikari@pcampus.edu.np</v>
       </c>
-      <c r="B3" t="str">
+      <c r="E3" t="str">
         <v>Test@123Password</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Nanda Bikram</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Adhikari</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Prof. Dr.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>baburam.dawadi@pcampus.edu.np</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Test@123Password</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Babu Ram</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Dawadi</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>